--- a/data/extra_material/task_solving_output_rating.xlsx
+++ b/data/extra_material/task_solving_output_rating.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\Chatbot-Evaluation-Framework\data\extra_material\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faufr\Documents\GitHub\CEP-guide\data\extra_material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B93A7B-EC10-4F9D-AA85-6F5C4CD084EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFA4876-088F-404A-993B-7985E7CE9F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>ID</t>
   </si>
@@ -43,6 +43,15 @@
   </si>
   <si>
     <t>How helpful did you find the chatbot's responses for solving the problem?</t>
+  </si>
+  <si>
+    <t>Scale</t>
+  </si>
+  <si>
+    <t>Not very confident (1); Not confident (2);  Neutral (3);  Confident (4);  Very confident (5)</t>
+  </si>
+  <si>
+    <t>Not very helpful (1); Not helpful (2);  Neutral (3);  Helpful (4);  Very helpful (5)</t>
   </si>
 </sst>
 </file>
@@ -369,35 +378,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="104.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
